--- a/Users_Database.xlsx
+++ b/Users_Database.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>name</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>permissions</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -444,10 +449,8 @@
           <t>admin</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B2" t="n">
+        <v>123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -457,6 +460,11 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>مدیرعامل محترم</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
         </is>
       </c>
     </row>
@@ -466,10 +474,8 @@
           <t>it</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B3" t="n">
+        <v>123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -479,6 +485,11 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>امین (مسئول فناوری / IT)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
         </is>
       </c>
     </row>
@@ -488,10 +499,8 @@
           <t>sales</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B4" t="n">
+        <v>123</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -501,6 +510,11 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>آقای اسماعیلی (مسئول فروش)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
         </is>
       </c>
     </row>
@@ -510,10 +524,8 @@
           <t>warehouse</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B5" t="n">
+        <v>123</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -523,6 +535,11 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>مسئول انبار</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
         </is>
       </c>
     </row>
@@ -532,10 +549,8 @@
           <t>mps</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B6" t="n">
+        <v>123</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -545,6 +560,11 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>برنامه‌ریز ارشد تولید</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
         </is>
       </c>
     </row>
@@ -554,10 +574,8 @@
           <t>workshop</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B7" t="n">
+        <v>123</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -567,6 +585,11 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>سرپرست خط تولید</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
         </is>
       </c>
     </row>
@@ -576,10 +599,8 @@
           <t>qc</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="B8" t="n">
+        <v>123</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -589,6 +610,38 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>مسئول ارشد کنترل کیفی (QC)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Amin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Amin1385</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ترکیبی</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اقای مودب </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ثبت سفارش,کارتابل مشتریان,مدیریت سفارشات,برنامه‌ریزی تولید,تولید و کارگاه,انباردار,کنترل کیفیت,گزارشات کلیدی,مدیریت کاربران</t>
         </is>
       </c>
     </row>
